--- a/artfynd/A 11002-2022 artfynd.xlsx
+++ b/artfynd/A 11002-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11002-2022 artfynd.xlsx
+++ b/artfynd/A 11002-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104020648</v>
+        <v>104020675</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548644.3821016114</v>
+        <v>548386</v>
       </c>
       <c r="R2" t="n">
-        <v>6984537.504270592</v>
+        <v>6984355</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104020620</v>
+        <v>104020681</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548497.5973745297</v>
+        <v>548201</v>
       </c>
       <c r="R3" t="n">
-        <v>6984121.559846499</v>
+        <v>6984363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104020673</v>
+        <v>104020671</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548356.2303483598</v>
+        <v>548414</v>
       </c>
       <c r="R4" t="n">
-        <v>6984319.978425851</v>
+        <v>6984357</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,6 +1018,1369 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104020620</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>548498</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6984122</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104020637</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>548321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6984335</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104020666</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>548399</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6984371</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104020673</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>548356</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6984320</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104020644</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>548194</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6984355</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104020648</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>548644</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6984538</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>62784235</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>548660</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6984531</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lisa Linck</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104020605</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>548422</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6984117</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104020627</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>548322</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6984337</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104020653</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>548227</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6984329</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104020618</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Åsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>548411</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6984358</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>62784324</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sönnerstmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>548394</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6984355</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2016-07-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lisa Linck</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Myrskyddsplaneinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 11002-2022 artfynd.xlsx
+++ b/artfynd/A 11002-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020675</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020681</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020671</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020637</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020666</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020673</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020644</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020648</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1815,6 +1865,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62784235</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1931,6 +1986,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020605</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020627</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2163,6 +2228,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020653</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020618</t>
         </is>
       </c>
     </row>
@@ -2383,8 +2458,30 @@
           <t>Myrskyddsplaneinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62784324</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>